--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121407645</v>
+        <v>121407660</v>
       </c>
       <c r="B2" t="n">
-        <v>94377</v>
+        <v>91259</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>3884</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623201</v>
+        <v>623200</v>
       </c>
       <c r="R2" t="n">
-        <v>6526700</v>
+        <v>6526650</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121407660</v>
+        <v>121407645</v>
       </c>
       <c r="B3" t="n">
-        <v>91247</v>
+        <v>94389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623200</v>
+        <v>623201</v>
       </c>
       <c r="R3" t="n">
-        <v>6526650</v>
+        <v>6526700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,6 +885,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121498376</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91260</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sandstugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>623197</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6526654</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Noterad</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Grusell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Grusell, Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121407660</v>
+        <v>121501662</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>94620</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandstugan, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623200</v>
+        <v>623208</v>
       </c>
       <c r="R2" t="n">
-        <v>6526650</v>
+        <v>6526661</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +773,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Grusell, Ursula Zinko</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121407645</v>
+        <v>121502682</v>
       </c>
       <c r="B3" t="n">
-        <v>94389</v>
+        <v>90724</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,27 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623201</v>
+        <v>623162</v>
       </c>
       <c r="R3" t="n">
-        <v>6526700</v>
+        <v>6526637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-30</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,121 +898,10 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Grusell, Ursula Zinko</t>
+          <t>Eva Grusell, Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>121498376</v>
-      </c>
-      <c r="B4" t="n">
-        <v>91260</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>3884</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Hasselticka</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Dichomitus campestris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Sandstugan, Srm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>623197</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6526654</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Nyköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Runtuna</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-11-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Noterad</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Eva Grusell</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Eva Grusell, Ursula Zinko</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121501662</v>
+        <v>121502682</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>90724</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Sandstugan, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623208</v>
+        <v>623162</v>
       </c>
       <c r="R2" t="n">
-        <v>6526661</v>
+        <v>6526637</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,19 +759,9 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,28 +770,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Eva Grusell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Eva Grusell, Bo Karlsson, Rolf Olsson, Göran Ekström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121502682</v>
+        <v>121501662</v>
       </c>
       <c r="B3" t="n">
-        <v>90724</v>
+        <v>94620</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,48 +805,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sandstugan, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623162</v>
+        <v>623208</v>
       </c>
       <c r="R3" t="n">
-        <v>6526637</v>
+        <v>6526661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,9 +866,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,19 +887,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Grusell</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Grusell, Bo Karlsson, Rolf Olsson, Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501662</v>
+        <v>121537167</v>
       </c>
       <c r="B3" t="n">
-        <v>94620</v>
+        <v>5464</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,41 +805,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>101377</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R3" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,19 +875,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,21 +891,539 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121501662</v>
+      </c>
+      <c r="B4" t="n">
+        <v>94620</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>623208</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6526661</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Göran Ekström</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121537128</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91118</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövsund ca 1 km so, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>623199</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6526556</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>signalart</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121537165</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43710</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>623165</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6526604</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>i några fnösktickor på björklågor</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121537205</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4775</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>623230</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6526694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Runtuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>i gammal grov levande gran</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -920,14 +920,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501662</v>
+        <v>121537128</v>
       </c>
       <c r="B4" t="n">
-        <v>94620</v>
+        <v>91118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -936,41 +936,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623208</v>
+        <v>623199</v>
       </c>
       <c r="R4" t="n">
-        <v>6526661</v>
+        <v>6526556</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,19 +1004,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,32 +1020,43 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537128</v>
+        <v>121501662</v>
       </c>
       <c r="B5" t="n">
-        <v>91118</v>
+        <v>94620</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1052,48 +1065,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623199</v>
+        <v>623208</v>
       </c>
       <c r="R5" t="n">
-        <v>6526556</v>
+        <v>6526661</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,14 +1126,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>signalart</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,29 +1147,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121502682</v>
       </c>
       <c r="B2" t="n">
-        <v>90724</v>
+        <v>90730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537167</v>
+        <v>121537128</v>
       </c>
       <c r="B3" t="n">
-        <v>5464</v>
+        <v>91124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,50 +805,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101377</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R3" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,14 +918,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537128</v>
+        <v>121501662</v>
       </c>
       <c r="B4" t="n">
-        <v>91118</v>
+        <v>94626</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -936,48 +934,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623199</v>
+        <v>623208</v>
       </c>
       <c r="R4" t="n">
-        <v>6526556</v>
+        <v>6526661</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,14 +995,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>signalart</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,43 +1016,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501662</v>
+        <v>121537167</v>
       </c>
       <c r="B5" t="n">
-        <v>94620</v>
+        <v>5464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,41 +1050,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>101377</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R5" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,19 +1120,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,18 +1136,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1168,7 +1168,7 @@
         <v>121537165</v>
       </c>
       <c r="B6" t="n">
-        <v>43710</v>
+        <v>43711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121502682</v>
       </c>
       <c r="B2" t="n">
-        <v>90730</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537128</v>
+        <v>121537165</v>
       </c>
       <c r="B3" t="n">
-        <v>91124</v>
+        <v>43711</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,48 +805,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R3" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,14 +920,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121501662</v>
+        <v>121537167</v>
       </c>
       <c r="B4" t="n">
-        <v>94626</v>
+        <v>5464</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -934,41 +936,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2818</v>
+        <v>101377</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R4" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,19 +1006,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,32 +1022,43 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537167</v>
+        <v>121501662</v>
       </c>
       <c r="B5" t="n">
-        <v>5464</v>
+        <v>94627</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1050,50 +1067,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101377</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623165</v>
+        <v>623208</v>
       </c>
       <c r="R5" t="n">
-        <v>6526604</v>
+        <v>6526661</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,14 +1128,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i björklågor</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,39 +1149,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B6" t="n">
-        <v>43711</v>
+        <v>91125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,50 +1183,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R6" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B3" t="n">
-        <v>43711</v>
+        <v>91125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,50 +805,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R3" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537167</v>
+        <v>121537165</v>
       </c>
       <c r="B4" t="n">
-        <v>5464</v>
+        <v>43711</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101377</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1013,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1167,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537128</v>
+        <v>121537167</v>
       </c>
       <c r="B6" t="n">
-        <v>91125</v>
+        <v>5464</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,48 +1181,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>101377</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R6" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537128</v>
+        <v>121501662</v>
       </c>
       <c r="B3" t="n">
-        <v>91125</v>
+        <v>94627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -805,48 +805,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623199</v>
+        <v>623208</v>
       </c>
       <c r="R3" t="n">
-        <v>6526556</v>
+        <v>6526661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,14 +866,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>signalart</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,39 +887,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B4" t="n">
-        <v>43711</v>
+        <v>91125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,50 +921,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R4" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +996,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,14 +1034,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501662</v>
+        <v>121537165</v>
       </c>
       <c r="B5" t="n">
-        <v>94627</v>
+        <v>43711</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,41 +1050,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R5" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,19 +1120,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,18 +1136,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501662</v>
+        <v>121537165</v>
       </c>
       <c r="B3" t="n">
-        <v>94627</v>
+        <v>43711</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -805,41 +805,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>101735</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R3" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,19 +875,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,18 +891,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1034,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537165</v>
+        <v>121537205</v>
       </c>
       <c r="B5" t="n">
-        <v>43711</v>
+        <v>4775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,21 +1065,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,7 +1088,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1083,17 +1098,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623165</v>
+        <v>623230</v>
       </c>
       <c r="R5" t="n">
-        <v>6526604</v>
+        <v>6526694</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,7 +1142,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1296,14 +1311,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121537205</v>
+        <v>121501662</v>
       </c>
       <c r="B7" t="n">
-        <v>4775</v>
+        <v>94627</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1312,50 +1327,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623230</v>
+        <v>623208</v>
       </c>
       <c r="R7" t="n">
-        <v>6526694</v>
+        <v>6526661</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,14 +1388,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>i gammal grov levande gran</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,29 +1409,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121502682</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537165</v>
+        <v>121537205</v>
       </c>
       <c r="B3" t="n">
-        <v>43711</v>
+        <v>4776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -838,17 +838,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623165</v>
+        <v>623230</v>
       </c>
       <c r="R3" t="n">
-        <v>6526604</v>
+        <v>6526694</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537128</v>
+        <v>121537165</v>
       </c>
       <c r="B4" t="n">
-        <v>91125</v>
+        <v>43712</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,48 +936,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R4" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,14 +1051,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537205</v>
+        <v>121501662</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>94635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,50 +1067,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623230</v>
+        <v>623208</v>
       </c>
       <c r="R5" t="n">
-        <v>6526694</v>
+        <v>6526661</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,14 +1128,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i gammal grov levande gran</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,39 +1149,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537167</v>
+        <v>121537128</v>
       </c>
       <c r="B6" t="n">
-        <v>5464</v>
+        <v>91133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,50 +1183,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101377</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R6" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,14 +1296,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501662</v>
+        <v>121537167</v>
       </c>
       <c r="B7" t="n">
-        <v>94627</v>
+        <v>5465</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1327,41 +1312,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>101377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R7" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,19 +1382,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,18 +1398,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537128</v>
+        <v>121501662</v>
       </c>
       <c r="B3" t="n">
-        <v>91133</v>
+        <v>94635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -805,48 +805,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623199</v>
+        <v>623208</v>
       </c>
       <c r="R3" t="n">
-        <v>6526556</v>
+        <v>6526661</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,14 +866,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>signalart</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,39 +887,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537205</v>
+        <v>121537167</v>
       </c>
       <c r="B4" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,7 +944,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -967,17 +954,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623230</v>
+        <v>623165</v>
       </c>
       <c r="R4" t="n">
-        <v>6526694</v>
+        <v>6526604</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i gammal grov levande gran</t>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537167</v>
+        <v>121537165</v>
       </c>
       <c r="B5" t="n">
-        <v>5465</v>
+        <v>43712</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,21 +1052,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101377</v>
+        <v>101735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1142,7 +1129,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,14 +1167,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121501662</v>
+        <v>121537205</v>
       </c>
       <c r="B6" t="n">
-        <v>94635</v>
+        <v>4776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1196,41 +1183,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623208</v>
+        <v>623230</v>
       </c>
       <c r="R6" t="n">
-        <v>6526661</v>
+        <v>6526694</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1257,19 +1253,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,28 +1269,39 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B7" t="n">
-        <v>43712</v>
+        <v>91133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,50 +1314,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R7" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,14 +789,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121501662</v>
+        <v>121537128</v>
       </c>
       <c r="B3" t="n">
-        <v>94635</v>
+        <v>91133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -805,41 +805,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623208</v>
+        <v>623199</v>
       </c>
       <c r="R3" t="n">
-        <v>6526661</v>
+        <v>6526556</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,19 +873,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,28 +889,39 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537167</v>
+        <v>121537165</v>
       </c>
       <c r="B4" t="n">
-        <v>5465</v>
+        <v>43712</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101377</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -998,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,14 +1049,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537165</v>
+        <v>121501662</v>
       </c>
       <c r="B5" t="n">
-        <v>43712</v>
+        <v>94635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1052,50 +1065,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623165</v>
+        <v>623208</v>
       </c>
       <c r="R5" t="n">
-        <v>6526604</v>
+        <v>6526661</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,14 +1126,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i några fnösktickor på björklågor</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,39 +1147,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537205</v>
+        <v>121537167</v>
       </c>
       <c r="B6" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1206,7 +1204,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1216,17 +1214,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623230</v>
+        <v>623165</v>
       </c>
       <c r="R6" t="n">
-        <v>6526694</v>
+        <v>6526604</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1260,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i gammal grov levande gran</t>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121537128</v>
+        <v>121537205</v>
       </c>
       <c r="B7" t="n">
-        <v>91133</v>
+        <v>4776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1314,48 +1312,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623199</v>
+        <v>623230</v>
       </c>
       <c r="R7" t="n">
-        <v>6526556</v>
+        <v>6526694</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537167</v>
+        <v>121537205</v>
       </c>
       <c r="B6" t="n">
-        <v>5465</v>
+        <v>4776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101377</v>
+        <v>102306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1214,17 +1214,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623165</v>
+        <v>623230</v>
       </c>
       <c r="R6" t="n">
-        <v>6526604</v>
+        <v>6526694</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i björklågor</t>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121537205</v>
+        <v>121537167</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
+        <v>5465</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,21 +1312,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>101377</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1335,7 +1335,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623230</v>
+        <v>623165</v>
       </c>
       <c r="R7" t="n">
-        <v>6526694</v>
+        <v>6526604</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>i gammal grov levande gran</t>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537128</v>
+        <v>121537167</v>
       </c>
       <c r="B3" t="n">
-        <v>91133</v>
+        <v>5465</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,48 +805,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>101377</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R3" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B4" t="n">
-        <v>43712</v>
+        <v>91133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,50 +936,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R4" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,14 +1049,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501662</v>
+        <v>121537205</v>
       </c>
       <c r="B5" t="n">
-        <v>94635</v>
+        <v>4776</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,41 +1065,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623208</v>
+        <v>623230</v>
       </c>
       <c r="R5" t="n">
-        <v>6526661</v>
+        <v>6526694</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,19 +1135,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,28 +1151,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537205</v>
+        <v>121537165</v>
       </c>
       <c r="B6" t="n">
-        <v>4776</v>
+        <v>43712</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,21 +1196,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102306</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1204,7 +1219,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1214,17 +1229,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623230</v>
+        <v>623165</v>
       </c>
       <c r="R6" t="n">
-        <v>6526694</v>
+        <v>6526604</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1273,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i gammal grov levande gran</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,14 +1311,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121537167</v>
+        <v>121501662</v>
       </c>
       <c r="B7" t="n">
-        <v>5465</v>
+        <v>94635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1312,50 +1327,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101377</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623165</v>
+        <v>623208</v>
       </c>
       <c r="R7" t="n">
-        <v>6526604</v>
+        <v>6526661</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1382,14 +1388,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>i björklågor</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,29 +1409,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -920,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537128</v>
+        <v>121537165</v>
       </c>
       <c r="B4" t="n">
-        <v>91133</v>
+        <v>43712</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,48 +936,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>101735</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R4" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,7 +1013,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,14 +1051,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121537205</v>
+        <v>121501662</v>
       </c>
       <c r="B5" t="n">
-        <v>4776</v>
+        <v>94635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1065,50 +1067,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102306</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövsund 3 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623230</v>
+        <v>623208</v>
       </c>
       <c r="R5" t="n">
-        <v>6526694</v>
+        <v>6526661</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,14 +1128,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>i gammal grov levande gran</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,39 +1149,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B6" t="n">
-        <v>43712</v>
+        <v>91133</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,50 +1183,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R6" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,7 +1258,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1311,14 +1296,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121501662</v>
+        <v>121537205</v>
       </c>
       <c r="B7" t="n">
-        <v>94635</v>
+        <v>4776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1327,41 +1312,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 3 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623208</v>
+        <v>623230</v>
       </c>
       <c r="R7" t="n">
-        <v>6526661</v>
+        <v>6526694</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,19 +1382,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>i gammal grov levande gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,18 +1398,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121502682</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121537167</v>
+        <v>121501662</v>
       </c>
       <c r="B3" t="n">
-        <v>5465</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,50 +795,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101377</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623165</v>
+        <v>623208</v>
       </c>
       <c r="R3" t="n">
-        <v>6526604</v>
+        <v>6526661</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,14 +856,19 @@
           <t>2024-12-07</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>i björklågor</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,44 +877,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121537165</v>
+        <v>121537128</v>
       </c>
       <c r="B4" t="n">
-        <v>43712</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,50 +906,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101735</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lövsund 2 ca 1 km so, Srm</t>
+          <t>Lövsund ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623165</v>
+        <v>623199</v>
       </c>
       <c r="R4" t="n">
-        <v>6526604</v>
+        <v>6526556</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,7 +981,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>i några fnösktickor på björklågor</t>
+          <t>signalart</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121501662</v>
+        <v>121537167</v>
       </c>
       <c r="B5" t="n">
-        <v>94635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,41 +1030,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2818</v>
+        <v>101377</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcketorps gamla tomt, Bäcketorps gamla tomt, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623208</v>
+        <v>623165</v>
       </c>
       <c r="R5" t="n">
-        <v>6526661</v>
+        <v>6526604</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,19 +1100,14 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:59</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>i björklågor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,33 +1116,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson, Eva Grusell, Rolf Olsson</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121537128</v>
+        <v>121537165</v>
       </c>
       <c r="B6" t="n">
-        <v>91133</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,48 +1156,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövsund ca 1 km so, Srm</t>
+          <t>Lövsund 2 ca 1 km so, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623199</v>
+        <v>623165</v>
       </c>
       <c r="R6" t="n">
-        <v>6526556</v>
+        <v>6526604</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1233,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>signalart</t>
+          <t>i några fnösktickor på björklågor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1299,12 +1274,7 @@
         <v>121537205</v>
       </c>
       <c r="B7" t="n">
-        <v>4776</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 56099-2024 artfynd.xlsx
+++ b/artfynd/A 56099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121502682</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121501662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121537128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121537167</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121537165</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,8 +1424,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121537205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>